--- a/artfynd/A 54332-2024 artfynd.xlsx
+++ b/artfynd/A 54332-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,434 +1141,6 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>112606719</v>
-      </c>
-      <c r="B6" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Båtskärsnäs, Nb</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>885027</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7318743</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Kalix</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Nederkalix</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>112606723</v>
-      </c>
-      <c r="B7" t="n">
-        <v>81593</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Båtskärsnäs, Nb</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>885000</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7318581</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Kalix</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Nederkalix</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>112606720</v>
-      </c>
-      <c r="B8" t="n">
-        <v>81593</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Båtskärsnäs, Nb</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>885023</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7318730</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Kalix</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Nederkalix</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>112606721</v>
-      </c>
-      <c r="B9" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Båtskärsnäs, Nb</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>885012</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7318581</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Kalix</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Nederkalix</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54332-2024 artfynd.xlsx
+++ b/artfynd/A 54332-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104160169</v>
+        <v>112606720</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>884999.5153236033</v>
+        <v>885023</v>
       </c>
       <c r="R2" t="n">
-        <v>7318581.07197747</v>
+        <v>7318730</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,14 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104160166</v>
+        <v>112606723</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>885023.4864490516</v>
+        <v>885000</v>
       </c>
       <c r="R3" t="n">
-        <v>7318730.188447851</v>
+        <v>7318581</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,24 +845,14 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,53 +879,52 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104160168</v>
+        <v>121149356</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Båtskärsnäs, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>885012.4037739297</v>
+        <v>884877</v>
       </c>
       <c r="R4" t="n">
-        <v>7318581.149617388</v>
+        <v>7318912</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,27 +948,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,19 +985,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104160165</v>
+        <v>112606719</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1066,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>885027.1451346964</v>
+        <v>885028</v>
       </c>
       <c r="R5" t="n">
-        <v>7318743.150524797</v>
+        <v>7318743</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,24 +1053,14 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,6 +1084,108 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112606721</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Båtskärsnäs, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>885012</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7318581</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kalix</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nederkalix</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-09-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
